--- a/AMD.xlsx
+++ b/AMD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D656FC41-AD84-4FAF-9B7B-D6216F280112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{488A17AF-6B7E-4E23-9D92-9A31BD9B829A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="58390" yWindow="5030" windowWidth="17370" windowHeight="13000" activeTab="1" xr2:uid="{449F5976-BBB2-4D6E-9B28-E8B6EC62A528}"/>
+    <workbookView xWindow="500" yWindow="1650" windowWidth="20990" windowHeight="18600" activeTab="1" xr2:uid="{449F5976-BBB2-4D6E-9B28-E8B6EC62A528}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -625,14 +625,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>43189</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>600885</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>43189</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>600885</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>110751</xdr:rowOff>
     </xdr:to>
@@ -649,7 +649,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16393059" y="0"/>
+          <a:off x="18198668" y="0"/>
           <a:ext cx="0" cy="12286186"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -1468,28 +1468,24 @@
         <v>3240</v>
       </c>
       <c r="Y7" s="10">
-        <f>+U7*1.2</f>
-        <v>4258.8</v>
+        <v>4341</v>
       </c>
       <c r="Z7" s="10">
-        <f>+V7*1.3</f>
-        <v>5016.7</v>
+        <v>5380</v>
       </c>
       <c r="AA7" s="10">
-        <f>+W7*1.15</f>
-        <v>4225.0999999999995</v>
+        <v>5775</v>
       </c>
       <c r="AB7" s="10">
-        <f>+X7*1.15</f>
-        <v>3725.9999999999995</v>
+        <v>6718</v>
       </c>
       <c r="AC7" s="10">
         <f>+Y7*1.5</f>
-        <v>6388.2000000000007</v>
+        <v>6511.5</v>
       </c>
       <c r="AD7" s="10">
         <f>+Z7*1.6</f>
-        <v>8026.72</v>
+        <v>8608</v>
       </c>
       <c r="AW7" s="3">
         <v>6043</v>
@@ -1502,27 +1498,27 @@
       </c>
       <c r="AZ7" s="3">
         <f>SUM(W7:Z7)</f>
-        <v>16189.5</v>
+        <v>16635</v>
       </c>
       <c r="BA7" s="3">
         <f>SUM(AA7:AD7)</f>
-        <v>22366.02</v>
+        <v>27612.5</v>
       </c>
       <c r="BB7" s="3">
         <f>+BA7*1.5</f>
-        <v>33549.03</v>
+        <v>41418.75</v>
       </c>
       <c r="BC7" s="3">
         <f>+BB7*1.5</f>
-        <v>50323.544999999998</v>
+        <v>62128.125</v>
       </c>
       <c r="BD7" s="3">
         <f>+BC7*1.4</f>
-        <v>70452.962999999989</v>
+        <v>86979.375</v>
       </c>
       <c r="BE7" s="3">
         <f>+BD7*1.4</f>
-        <v>98634.148199999981</v>
+        <v>121771.12499999999</v>
       </c>
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.25">
@@ -1562,28 +1558,24 @@
         <v>2499</v>
       </c>
       <c r="Y8" s="10">
-        <f>+X8+200</f>
-        <v>2699</v>
+        <v>2750</v>
       </c>
       <c r="Z8" s="10">
-        <f>+V8*1.25</f>
-        <v>2891.25</v>
+        <v>3097</v>
       </c>
       <c r="AA8" s="10">
-        <f t="shared" ref="AA8:AA10" si="1">+W8*1.1</f>
-        <v>2523.4</v>
+        <v>2885</v>
       </c>
       <c r="AB8" s="10">
-        <f t="shared" ref="AB8:AB10" si="2">+X8*1.1</f>
-        <v>2748.9</v>
+        <v>3062</v>
       </c>
       <c r="AC8" s="10">
-        <f t="shared" ref="AC8:AC10" si="3">+Y8*1.1</f>
-        <v>2968.9</v>
+        <f t="shared" ref="AC8:AC10" si="1">+Y8*1.1</f>
+        <v>3025.0000000000005</v>
       </c>
       <c r="AD8" s="10">
         <f>+Z8*1.2</f>
-        <v>3469.5</v>
+        <v>3716.3999999999996</v>
       </c>
       <c r="AW8" s="3">
         <v>6201</v>
@@ -1596,27 +1588,27 @@
       </c>
       <c r="AZ8" s="3">
         <f>SUM(W8:Z8)</f>
-        <v>10383.25</v>
+        <v>10640</v>
       </c>
       <c r="BA8" s="3">
         <f>SUM(AA8:AD8)</f>
-        <v>11710.7</v>
+        <v>12688.4</v>
       </c>
       <c r="BB8" s="3">
         <f>+BA8*1.1</f>
-        <v>12881.770000000002</v>
+        <v>13957.240000000002</v>
       </c>
       <c r="BC8" s="3">
-        <f t="shared" ref="BC8:BE10" si="4">+BB8*1.1</f>
-        <v>14169.947000000004</v>
+        <f t="shared" ref="BC8:BE10" si="2">+BB8*1.1</f>
+        <v>15352.964000000004</v>
       </c>
       <c r="BD8" s="3">
-        <f t="shared" si="4"/>
-        <v>15586.941700000005</v>
+        <f t="shared" si="2"/>
+        <v>16888.260400000006</v>
       </c>
       <c r="BE8" s="3">
-        <f t="shared" si="4"/>
-        <v>17145.635870000006</v>
+        <f t="shared" si="2"/>
+        <v>18577.08644000001</v>
       </c>
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.25">
@@ -1659,28 +1651,24 @@
         <v>1122</v>
       </c>
       <c r="Y9" s="10">
-        <f>+X9+100</f>
-        <v>1222</v>
+        <v>1298</v>
       </c>
       <c r="Z9" s="10">
-        <f>+V9*1.2</f>
-        <v>675.6</v>
+        <v>843</v>
       </c>
       <c r="AA9" s="10">
+        <v>720</v>
+      </c>
+      <c r="AB9" s="10">
+        <v>779</v>
+      </c>
+      <c r="AC9" s="10">
         <f t="shared" si="1"/>
-        <v>711.7</v>
-      </c>
-      <c r="AB9" s="10">
-        <f t="shared" si="2"/>
-        <v>1234.2</v>
-      </c>
-      <c r="AC9" s="10">
-        <f t="shared" si="3"/>
-        <v>1344.2</v>
+        <v>1427.8000000000002</v>
       </c>
       <c r="AD9" s="10">
         <f>+Z9*1.2</f>
-        <v>810.72</v>
+        <v>1011.5999999999999</v>
       </c>
       <c r="AW9" s="3">
         <v>6805</v>
@@ -1693,27 +1681,27 @@
       </c>
       <c r="AZ9" s="3">
         <f>SUM(W9:Z9)</f>
-        <v>3666.6</v>
+        <v>3910</v>
       </c>
       <c r="BA9" s="3">
         <f>SUM(AA9:AD9)</f>
-        <v>4100.8200000000006</v>
+        <v>3938.4</v>
       </c>
       <c r="BB9" s="3">
-        <f t="shared" ref="BB9" si="5">+BA9*1.1</f>
-        <v>4510.902000000001</v>
+        <f t="shared" ref="BB9" si="3">+BA9*1.1</f>
+        <v>4332.2400000000007</v>
       </c>
       <c r="BC9" s="3">
-        <f t="shared" si="4"/>
-        <v>4961.9922000000015</v>
+        <f t="shared" si="2"/>
+        <v>4765.4640000000009</v>
       </c>
       <c r="BD9" s="3">
-        <f t="shared" si="4"/>
-        <v>5458.1914200000019</v>
+        <f t="shared" si="2"/>
+        <v>5242.010400000001</v>
       </c>
       <c r="BE9" s="3">
-        <f t="shared" si="4"/>
-        <v>6004.0105620000022</v>
+        <f t="shared" si="2"/>
+        <v>5766.2114400000019</v>
       </c>
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.25">
@@ -1756,28 +1744,24 @@
         <v>824</v>
       </c>
       <c r="Y10" s="10">
-        <f>+U10*1.1</f>
-        <v>1019.7</v>
+        <v>857</v>
       </c>
       <c r="Z10" s="10">
-        <f>+V10*1.15</f>
-        <v>1061.4499999999998</v>
+        <v>950</v>
       </c>
       <c r="AA10" s="10">
+        <v>873</v>
+      </c>
+      <c r="AB10" s="10">
+        <v>977</v>
+      </c>
+      <c r="AC10" s="10">
         <f t="shared" si="1"/>
-        <v>905.30000000000007</v>
-      </c>
-      <c r="AB10" s="10">
-        <f t="shared" si="2"/>
-        <v>906.40000000000009</v>
-      </c>
-      <c r="AC10" s="10">
-        <f t="shared" si="3"/>
-        <v>1121.67</v>
+        <v>942.7</v>
       </c>
       <c r="AD10" s="10">
         <f>+Z10*1.2</f>
-        <v>1273.7399999999998</v>
+        <v>1140</v>
       </c>
       <c r="AW10" s="3">
         <v>4552</v>
@@ -1790,27 +1774,27 @@
       </c>
       <c r="AZ10" s="3">
         <f>SUM(W10:Z10)</f>
-        <v>3728.1499999999996</v>
+        <v>3454</v>
       </c>
       <c r="BA10" s="3">
         <f>SUM(AA10:AD10)</f>
-        <v>4207.1100000000006</v>
+        <v>3932.7</v>
       </c>
       <c r="BB10" s="3">
-        <f t="shared" ref="BB10" si="6">+BA10*1.1</f>
-        <v>4627.8210000000008</v>
+        <f t="shared" ref="BB10" si="4">+BA10*1.1</f>
+        <v>4325.97</v>
       </c>
       <c r="BC10" s="3">
-        <f t="shared" si="4"/>
-        <v>5090.6031000000012</v>
+        <f t="shared" si="2"/>
+        <v>4758.5670000000009</v>
       </c>
       <c r="BD10" s="3">
-        <f t="shared" si="4"/>
-        <v>5599.6634100000019</v>
+        <f t="shared" si="2"/>
+        <v>5234.4237000000012</v>
       </c>
       <c r="BE10" s="3">
-        <f t="shared" si="4"/>
-        <v>6159.6297510000022</v>
+        <f t="shared" si="2"/>
+        <v>5757.8660700000019</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.25">
@@ -1852,47 +1836,55 @@
         <v>5800</v>
       </c>
       <c r="R12" s="9">
-        <f>+AX12-Q12-P12-O12</f>
+        <f>SUM(R7:R10)</f>
         <v>6168</v>
       </c>
       <c r="S12" s="9">
+        <f>SUM(S7:S10)</f>
         <v>5473</v>
       </c>
       <c r="T12" s="9">
+        <f>SUM(T7:T10)</f>
         <v>5835</v>
       </c>
       <c r="U12" s="9">
+        <f>SUM(U7:U10)</f>
         <v>6819</v>
       </c>
       <c r="V12" s="9">
+        <f>SUM(V7:V10)</f>
         <v>7658</v>
       </c>
       <c r="W12" s="9">
+        <f>SUM(W7:W10)</f>
         <v>7438</v>
       </c>
       <c r="X12" s="9">
+        <f>SUM(X7:X10)</f>
         <v>7685</v>
       </c>
       <c r="Y12" s="9">
+        <f>SUM(Y7:Y10)</f>
         <v>9246</v>
       </c>
       <c r="Z12" s="9">
         <f>SUM(Z7:Z10)</f>
-        <v>9645</v>
+        <v>10270</v>
       </c>
       <c r="AA12" s="9">
-        <v>8850</v>
+        <f>SUM(AA7:AA10)</f>
+        <v>10253</v>
       </c>
       <c r="AB12" s="9">
-        <v>9530</v>
+        <f>SUM(AB7:AB10)</f>
+        <v>11536</v>
       </c>
       <c r="AC12" s="9">
-        <f>SUM(AC7:AC10)</f>
-        <v>11822.970000000001</v>
+        <v>13000</v>
       </c>
       <c r="AD12" s="9">
         <f>SUM(AD7:AD10)</f>
-        <v>13580.68</v>
+        <v>14476</v>
       </c>
       <c r="AE12" s="5"/>
       <c r="AF12" s="5"/>
@@ -1937,47 +1929,47 @@
       </c>
       <c r="AZ12" s="6">
         <f>SUM(W12:Z12)</f>
-        <v>34014</v>
+        <v>34639</v>
       </c>
       <c r="BA12" s="6">
-        <f t="shared" ref="BA12:BB12" si="7">SUM(BA7:BA10)</f>
-        <v>42384.65</v>
+        <f t="shared" ref="BA12:BB12" si="5">SUM(BA7:BA10)</f>
+        <v>48172</v>
       </c>
       <c r="BB12" s="6">
-        <f t="shared" si="7"/>
-        <v>55569.523000000008</v>
+        <f t="shared" si="5"/>
+        <v>64034.200000000004</v>
       </c>
       <c r="BC12" s="6">
         <f>SUM(BC7:BC10)</f>
-        <v>74546.087300000014</v>
+        <v>87005.12000000001</v>
       </c>
       <c r="BD12" s="6">
         <f>SUM(BD7:BD10)</f>
-        <v>97097.75953000001</v>
+        <v>114344.0695</v>
       </c>
       <c r="BE12" s="6">
         <f>SUM(BE7:BE10)</f>
-        <v>127943.42438299999</v>
+        <v>151872.28894999999</v>
       </c>
       <c r="BF12" s="6">
         <f>+BE12*1.05</f>
-        <v>134340.59560214999</v>
+        <v>159465.90339749999</v>
       </c>
       <c r="BG12" s="6">
         <f>+BF12*1.05</f>
-        <v>141057.62538225748</v>
+        <v>167439.19856737499</v>
       </c>
       <c r="BH12" s="6">
         <f>+BG12*1.05</f>
-        <v>148110.50665137035</v>
+        <v>175811.15849574376</v>
       </c>
       <c r="BI12" s="6">
         <f>+BH12*1.05</f>
-        <v>155516.03198393888</v>
+        <v>184601.71642053095</v>
       </c>
       <c r="BJ12" s="6">
         <f>+BI12*1.05</f>
-        <v>163291.83358313583</v>
+        <v>193831.80224155751</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.25">
@@ -2036,24 +2028,21 @@
         <v>4206</v>
       </c>
       <c r="Z13" s="10">
-        <f t="shared" ref="Y13:AC13" si="8">+Z12-Z14</f>
-        <v>4436.7</v>
+        <v>4433</v>
       </c>
       <c r="AA13" s="10">
-        <f t="shared" si="8"/>
-        <v>4071</v>
+        <v>4576</v>
       </c>
       <c r="AB13" s="10">
-        <f t="shared" si="8"/>
-        <v>4383.7999999999993</v>
+        <v>5073</v>
       </c>
       <c r="AC13" s="10">
-        <f t="shared" si="8"/>
-        <v>5438.5662000000002</v>
+        <f t="shared" ref="AC13" si="6">+AC12-AC14</f>
+        <v>5979.9999999999991</v>
       </c>
       <c r="AD13" s="10">
         <f>+AD12-AD14</f>
-        <v>6247.1127999999999</v>
+        <v>6658.9599999999991</v>
       </c>
       <c r="AR13" s="3">
         <v>3466</v>
@@ -2082,47 +2071,47 @@
       </c>
       <c r="AZ13" s="3">
         <f>+AZ12-AZ14</f>
-        <v>15986.579999999998</v>
+        <v>16280.329999999998</v>
       </c>
       <c r="BA13" s="3">
         <f>+BA12-BA14</f>
-        <v>19920.785499999998</v>
+        <v>22640.84</v>
       </c>
       <c r="BB13" s="3">
-        <f t="shared" ref="BB13:BJ13" si="9">+BB12-BB14</f>
-        <v>26117.675810000001</v>
+        <f t="shared" ref="BB13:BJ13" si="7">+BB12-BB14</f>
+        <v>30096.074000000001</v>
       </c>
       <c r="BC13" s="3">
-        <f t="shared" si="9"/>
-        <v>35036.661031000003</v>
+        <f t="shared" si="7"/>
+        <v>40892.4064</v>
       </c>
       <c r="BD13" s="3">
-        <f t="shared" si="9"/>
-        <v>45635.946979100001</v>
+        <f t="shared" si="7"/>
+        <v>53741.712664999999</v>
       </c>
       <c r="BE13" s="3">
-        <f t="shared" si="9"/>
-        <v>60133.409460009992</v>
+        <f t="shared" si="7"/>
+        <v>71379.975806499991</v>
       </c>
       <c r="BF13" s="3">
-        <f t="shared" si="9"/>
-        <v>63140.079933010493</v>
+        <f t="shared" si="7"/>
+        <v>74948.974596824992</v>
       </c>
       <c r="BG13" s="3">
-        <f t="shared" si="9"/>
-        <v>66297.083929661007</v>
+        <f t="shared" si="7"/>
+        <v>78696.423326666234</v>
       </c>
       <c r="BH13" s="3">
-        <f t="shared" si="9"/>
-        <v>69611.938126144058</v>
+        <f t="shared" si="7"/>
+        <v>82631.244492999569</v>
       </c>
       <c r="BI13" s="3">
-        <f t="shared" si="9"/>
-        <v>73092.535032451269</v>
+        <f t="shared" si="7"/>
+        <v>86762.806717649539</v>
       </c>
       <c r="BJ13" s="3">
-        <f t="shared" si="9"/>
-        <v>76747.161784073833</v>
+        <f t="shared" si="7"/>
+        <v>91100.947053532029</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.25">
@@ -2147,23 +2136,23 @@
         <v>2846</v>
       </c>
       <c r="O14" s="10">
-        <f t="shared" ref="O14:S14" si="10">O12-O13</f>
+        <f t="shared" ref="O14:S14" si="8">O12-O13</f>
         <v>2664</v>
       </c>
       <c r="P14" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2655</v>
       </c>
       <c r="Q14" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2957</v>
       </c>
       <c r="R14" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>3126</v>
       </c>
       <c r="S14" s="10">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>2790</v>
       </c>
       <c r="T14" s="10">
@@ -2188,51 +2177,51 @@
         <v>5040</v>
       </c>
       <c r="Z14" s="10">
-        <f t="shared" ref="Y14:AD14" si="11">+Z12*0.54</f>
-        <v>5208.3</v>
+        <f>+Z12-Z13</f>
+        <v>5837</v>
       </c>
       <c r="AA14" s="10">
-        <f t="shared" si="11"/>
-        <v>4779</v>
+        <f>+AA12-AA13</f>
+        <v>5677</v>
       </c>
       <c r="AB14" s="10">
-        <f t="shared" si="11"/>
-        <v>5146.2000000000007</v>
+        <f>+AB12-AB13</f>
+        <v>6463</v>
       </c>
       <c r="AC14" s="10">
-        <f t="shared" si="11"/>
-        <v>6384.403800000001</v>
+        <f t="shared" ref="AC14:AD14" si="9">+AC12*0.54</f>
+        <v>7020.0000000000009</v>
       </c>
       <c r="AD14" s="10">
-        <f t="shared" si="11"/>
-        <v>7333.5672000000004</v>
+        <f t="shared" si="9"/>
+        <v>7817.0400000000009</v>
       </c>
       <c r="AR14" s="3">
-        <f t="shared" ref="AR14:AX14" si="12">+AR12-AR13</f>
+        <f t="shared" ref="AR14:AX14" si="10">+AR12-AR13</f>
         <v>1863</v>
       </c>
       <c r="AS14" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2447</v>
       </c>
       <c r="AT14" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>2868</v>
       </c>
       <c r="AU14" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>4347</v>
       </c>
       <c r="AV14" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>7929</v>
       </c>
       <c r="AW14" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>12051</v>
       </c>
       <c r="AX14" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>11402</v>
       </c>
       <c r="AY14" s="3">
@@ -2241,47 +2230,47 @@
       </c>
       <c r="AZ14" s="3">
         <f>+AZ12*0.53</f>
-        <v>18027.420000000002</v>
+        <v>18358.670000000002</v>
       </c>
       <c r="BA14" s="3">
         <f>+BA12*0.53</f>
-        <v>22463.864500000003</v>
+        <v>25531.16</v>
       </c>
       <c r="BB14" s="3">
-        <f t="shared" ref="BB14:BJ14" si="13">+BB12*0.53</f>
-        <v>29451.847190000008</v>
+        <f t="shared" ref="BB14:BJ14" si="11">+BB12*0.53</f>
+        <v>33938.126000000004</v>
       </c>
       <c r="BC14" s="3">
-        <f t="shared" si="13"/>
-        <v>39509.426269000011</v>
+        <f t="shared" si="11"/>
+        <v>46112.71360000001</v>
       </c>
       <c r="BD14" s="3">
-        <f t="shared" si="13"/>
-        <v>51461.812550900009</v>
+        <f t="shared" si="11"/>
+        <v>60602.356834999999</v>
       </c>
       <c r="BE14" s="3">
-        <f t="shared" si="13"/>
-        <v>67810.014922989998</v>
+        <f t="shared" si="11"/>
+        <v>80492.313143499996</v>
       </c>
       <c r="BF14" s="3">
-        <f t="shared" si="13"/>
-        <v>71200.515669139495</v>
+        <f t="shared" si="11"/>
+        <v>84516.928800674999</v>
       </c>
       <c r="BG14" s="3">
-        <f t="shared" si="13"/>
-        <v>74760.541452596473</v>
+        <f t="shared" si="11"/>
+        <v>88742.775240708754</v>
       </c>
       <c r="BH14" s="3">
-        <f t="shared" si="13"/>
-        <v>78498.568525226292</v>
+        <f t="shared" si="11"/>
+        <v>93179.91400274419</v>
       </c>
       <c r="BI14" s="3">
-        <f t="shared" si="13"/>
-        <v>82423.496951487614</v>
+        <f t="shared" si="11"/>
+        <v>97838.909702881414</v>
       </c>
       <c r="BJ14" s="3">
-        <f t="shared" si="13"/>
-        <v>86544.671799061995</v>
+        <f t="shared" si="11"/>
+        <v>102730.85518802548</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.25">
@@ -2299,7 +2288,7 @@
         <v>1279</v>
       </c>
       <c r="N15" s="10">
-        <f t="shared" ref="N15:N16" si="14">+AW15-M15-L15-K15</f>
+        <f t="shared" ref="N15:N16" si="12">+AW15-M15-L15-K15</f>
         <v>1366</v>
       </c>
       <c r="O15" s="10">
@@ -2337,24 +2326,21 @@
         <v>2139</v>
       </c>
       <c r="Z15" s="10">
-        <f t="shared" ref="Z15:Z16" si="15">+V15*1.1</f>
-        <v>1883.2</v>
+        <v>2330</v>
       </c>
       <c r="AA15" s="10">
-        <f t="shared" ref="AA15:AA16" si="16">+W15*1.1</f>
-        <v>1900.8000000000002</v>
+        <v>2397</v>
       </c>
       <c r="AB15" s="10">
-        <f t="shared" ref="AB15:AB16" si="17">+X15*1.1</f>
-        <v>2083.4</v>
+        <v>2528</v>
       </c>
       <c r="AC15" s="10">
-        <f t="shared" ref="AC15:AC16" si="18">+Y15*1.1</f>
+        <f t="shared" ref="AC15:AC16" si="13">+Y15*1.1</f>
         <v>2352.9</v>
       </c>
       <c r="AD15" s="10">
-        <f t="shared" ref="AD15:AD16" si="19">+Z15*1.1</f>
-        <v>2071.5200000000004</v>
+        <f t="shared" ref="AD15:AD16" si="14">+Z15*1.1</f>
+        <v>2563</v>
       </c>
       <c r="AR15" s="3">
         <v>1196</v>
@@ -2378,7 +2364,7 @@
         <v>5872</v>
       </c>
       <c r="AY15" s="3">
-        <f t="shared" ref="AY15:AY16" si="20">SUM(S15:V15)</f>
+        <f t="shared" ref="AY15:AY16" si="15">SUM(S15:V15)</f>
         <v>6456</v>
       </c>
       <c r="AZ15" s="3">
@@ -2386,23 +2372,23 @@
         <v>7101.6</v>
       </c>
       <c r="BA15" s="3">
-        <f t="shared" ref="BA15:BE15" si="21">+AZ15*1.1</f>
+        <f t="shared" ref="BA15:BE15" si="16">+AZ15*1.1</f>
         <v>7811.7600000000011</v>
       </c>
       <c r="BB15" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>8592.9360000000015</v>
       </c>
       <c r="BC15" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>9452.2296000000024</v>
       </c>
       <c r="BD15" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>10397.452560000003</v>
       </c>
       <c r="BE15" s="3">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>11437.197816000005</v>
       </c>
     </row>
@@ -2421,7 +2407,7 @@
         <v>557</v>
       </c>
       <c r="N16" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>590</v>
       </c>
       <c r="O16" s="10">
@@ -2459,24 +2445,21 @@
         <v>1069</v>
       </c>
       <c r="Z16" s="10">
-        <f t="shared" si="15"/>
-        <v>871.2</v>
+        <v>1198</v>
       </c>
       <c r="AA16" s="10">
-        <f t="shared" si="16"/>
-        <v>974.6</v>
+        <v>1253</v>
       </c>
       <c r="AB16" s="10">
-        <f t="shared" si="17"/>
-        <v>1090.1000000000001</v>
+        <v>1401</v>
       </c>
       <c r="AC16" s="10">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>1175.9000000000001</v>
       </c>
       <c r="AD16" s="10">
-        <f t="shared" si="19"/>
-        <v>958.32000000000016</v>
+        <f t="shared" si="14"/>
+        <v>1317.8000000000002</v>
       </c>
       <c r="AR16" s="3">
         <v>516</v>
@@ -2500,31 +2483,31 @@
         <v>2352</v>
       </c>
       <c r="AY16" s="3">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>2783</v>
       </c>
       <c r="AZ16" s="3">
-        <f t="shared" ref="AZ16:BE16" si="22">+AY16*1.1</f>
+        <f t="shared" ref="AZ16:BE16" si="17">+AY16*1.1</f>
         <v>3061.3</v>
       </c>
       <c r="BA16" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="17"/>
         <v>3367.4300000000003</v>
       </c>
       <c r="BB16" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="17"/>
         <v>3704.1730000000007</v>
       </c>
       <c r="BC16" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="17"/>
         <v>4074.5903000000012</v>
       </c>
       <c r="BD16" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="17"/>
         <v>4482.0493300000016</v>
       </c>
       <c r="BE16" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="17"/>
         <v>4930.2542630000025</v>
       </c>
     </row>
@@ -2546,72 +2529,72 @@
         <v>1836</v>
       </c>
       <c r="N17" s="10">
-        <f t="shared" ref="N17" si="23">N15+N16</f>
+        <f t="shared" ref="N17" si="18">N15+N16</f>
         <v>1956</v>
       </c>
       <c r="O17" s="10">
-        <f t="shared" ref="O17:U17" si="24">O15+O16</f>
+        <f t="shared" ref="O17:U17" si="19">O15+O16</f>
         <v>1996</v>
       </c>
       <c r="P17" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>1990</v>
       </c>
       <c r="Q17" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>2083</v>
       </c>
       <c r="R17" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>2155</v>
       </c>
       <c r="S17" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>2145</v>
       </c>
       <c r="T17" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>2233</v>
       </c>
       <c r="U17" s="10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>2357</v>
       </c>
       <c r="V17" s="10">
-        <f t="shared" ref="V17:X17" si="25">V15+V16</f>
+        <f t="shared" ref="V17:X17" si="20">V15+V16</f>
         <v>2504</v>
       </c>
       <c r="W17" s="10">
-        <f t="shared" ref="W17" si="26">W15+W16</f>
+        <f t="shared" ref="W17" si="21">W15+W16</f>
         <v>2614</v>
       </c>
       <c r="X17" s="10">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>2885</v>
       </c>
       <c r="Y17" s="10">
-        <f t="shared" ref="Y17:AD17" si="27">Y15+Y16</f>
+        <f t="shared" ref="Y17:AD17" si="22">Y15+Y16</f>
         <v>3208</v>
       </c>
       <c r="Z17" s="10">
-        <f t="shared" si="27"/>
-        <v>2754.4</v>
+        <f t="shared" si="22"/>
+        <v>3528</v>
       </c>
       <c r="AA17" s="10">
-        <f t="shared" si="27"/>
-        <v>2875.4</v>
+        <f t="shared" si="22"/>
+        <v>3650</v>
       </c>
       <c r="AB17" s="10">
-        <f t="shared" si="27"/>
-        <v>3173.5</v>
+        <f t="shared" si="22"/>
+        <v>3929</v>
       </c>
       <c r="AC17" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="22"/>
         <v>3528.8</v>
       </c>
       <c r="AD17" s="10">
-        <f t="shared" si="27"/>
-        <v>3029.8400000000006</v>
+        <f t="shared" si="22"/>
+        <v>3880.8</v>
       </c>
       <c r="AR17" s="3">
         <f>+AR15+AR16</f>
@@ -2634,59 +2617,59 @@
         <v>4293</v>
       </c>
       <c r="AW17" s="3">
-        <f t="shared" ref="AW17:AX17" si="28">+AW15+AW16</f>
+        <f t="shared" ref="AW17:AX17" si="23">+AW15+AW16</f>
         <v>7341</v>
       </c>
       <c r="AX17" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="23"/>
         <v>8224</v>
       </c>
       <c r="AY17" s="3">
-        <f t="shared" ref="AY17:BA17" si="29">+AY15+AY16</f>
+        <f t="shared" ref="AY17:BA17" si="24">+AY15+AY16</f>
         <v>9239</v>
       </c>
       <c r="AZ17" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="24"/>
         <v>10162.900000000001</v>
       </c>
       <c r="BA17" s="3">
-        <f t="shared" si="29"/>
+        <f t="shared" si="24"/>
         <v>11179.190000000002</v>
       </c>
       <c r="BB17" s="3">
-        <f t="shared" ref="BB17:BJ17" si="30">+BB15+BB16</f>
+        <f t="shared" ref="BB17:BJ17" si="25">+BB15+BB16</f>
         <v>12297.109000000002</v>
       </c>
       <c r="BC17" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>13526.819900000004</v>
       </c>
       <c r="BD17" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>14879.501890000005</v>
       </c>
       <c r="BE17" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>16367.452079000008</v>
       </c>
       <c r="BF17" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BG17" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BH17" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BI17" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="BJ17" s="3">
-        <f t="shared" si="30"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
     </row>
@@ -2708,72 +2691,72 @@
         <v>930</v>
       </c>
       <c r="N18" s="10">
-        <f t="shared" ref="N18" si="31">N14-N17</f>
+        <f t="shared" ref="N18" si="26">N14-N17</f>
         <v>890</v>
       </c>
       <c r="O18" s="10">
-        <f t="shared" ref="O18:U18" si="32">O14-O17</f>
+        <f t="shared" ref="O18:U18" si="27">O14-O17</f>
         <v>668</v>
       </c>
       <c r="P18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v>665</v>
       </c>
       <c r="Q18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v>874</v>
       </c>
       <c r="R18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v>971</v>
       </c>
       <c r="S18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v>645</v>
       </c>
       <c r="T18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v>868</v>
       </c>
       <c r="U18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="27"/>
         <v>1295</v>
       </c>
       <c r="V18" s="10">
-        <f t="shared" ref="V18:X18" si="33">V14-V17</f>
+        <f t="shared" ref="V18:X18" si="28">V14-V17</f>
         <v>1630</v>
       </c>
       <c r="W18" s="10">
-        <f t="shared" ref="W18" si="34">W14-W17</f>
+        <f t="shared" ref="W18" si="29">W14-W17</f>
         <v>1378</v>
       </c>
       <c r="X18" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="28"/>
         <v>441</v>
       </c>
       <c r="Y18" s="10">
-        <f t="shared" ref="Y18:AD18" si="35">Y14-Y17</f>
+        <f t="shared" ref="Y18:AD18" si="30">Y14-Y17</f>
         <v>1832</v>
       </c>
       <c r="Z18" s="10">
-        <f t="shared" si="35"/>
-        <v>2453.9</v>
+        <f t="shared" si="30"/>
+        <v>2309</v>
       </c>
       <c r="AA18" s="10">
-        <f t="shared" si="35"/>
-        <v>1903.6</v>
+        <f t="shared" si="30"/>
+        <v>2027</v>
       </c>
       <c r="AB18" s="10">
-        <f t="shared" si="35"/>
-        <v>1972.7000000000007</v>
+        <f t="shared" si="30"/>
+        <v>2534</v>
       </c>
       <c r="AC18" s="10">
-        <f t="shared" si="35"/>
-        <v>2855.6038000000008</v>
+        <f t="shared" si="30"/>
+        <v>3491.2000000000007</v>
       </c>
       <c r="AD18" s="10">
-        <f t="shared" si="35"/>
-        <v>4303.7271999999994</v>
+        <f t="shared" si="30"/>
+        <v>3936.2400000000007</v>
       </c>
       <c r="AR18" s="3">
         <f>+AR14-AR17</f>
@@ -2796,60 +2779,60 @@
         <v>3636</v>
       </c>
       <c r="AW18" s="3">
-        <f t="shared" ref="AW18:AX18" si="36">+AW14-AW17</f>
+        <f t="shared" ref="AW18:AX18" si="31">+AW14-AW17</f>
         <v>4710</v>
       </c>
       <c r="AX18" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="31"/>
         <v>3178</v>
       </c>
       <c r="AY18" s="3">
-        <f t="shared" ref="AY18:BA18" si="37">+AY14-AY17</f>
+        <f t="shared" ref="AY18:BA18" si="32">+AY14-AY17</f>
         <v>4438</v>
       </c>
       <c r="AZ18" s="3">
-        <f t="shared" si="37"/>
-        <v>7864.52</v>
+        <f t="shared" si="32"/>
+        <v>8195.77</v>
       </c>
       <c r="BA18" s="3">
-        <f t="shared" si="37"/>
-        <v>11284.674500000001</v>
+        <f t="shared" si="32"/>
+        <v>14351.969999999998</v>
       </c>
       <c r="BB18" s="3">
-        <f t="shared" ref="BB18:BJ18" si="38">+BB14-BB17</f>
-        <v>17154.738190000004</v>
+        <f t="shared" ref="BB18:BJ18" si="33">+BB14-BB17</f>
+        <v>21641.017</v>
       </c>
       <c r="BC18" s="3">
-        <f t="shared" si="38"/>
-        <v>25982.606369000008</v>
+        <f t="shared" si="33"/>
+        <v>32585.893700000008</v>
       </c>
       <c r="BD18" s="3">
-        <f t="shared" si="38"/>
-        <v>36582.310660900002</v>
+        <f t="shared" si="33"/>
+        <v>45722.854944999992</v>
       </c>
       <c r="BE18" s="3">
-        <f t="shared" si="38"/>
-        <v>51442.562843989988</v>
+        <f t="shared" si="33"/>
+        <v>64124.861064499986</v>
       </c>
       <c r="BF18" s="3">
-        <f t="shared" si="38"/>
-        <v>71200.515669139495</v>
+        <f t="shared" si="33"/>
+        <v>84516.928800674999</v>
       </c>
       <c r="BG18" s="3">
-        <f t="shared" si="38"/>
-        <v>74760.541452596473</v>
+        <f t="shared" si="33"/>
+        <v>88742.775240708754</v>
       </c>
       <c r="BH18" s="3">
-        <f t="shared" si="38"/>
-        <v>78498.568525226292</v>
+        <f t="shared" si="33"/>
+        <v>93179.91400274419</v>
       </c>
       <c r="BI18" s="3">
-        <f t="shared" si="38"/>
-        <v>82423.496951487614</v>
+        <f t="shared" si="33"/>
+        <v>97838.909702881414</v>
       </c>
       <c r="BJ18" s="3">
-        <f t="shared" si="38"/>
-        <v>86544.671799061995</v>
+        <f t="shared" si="33"/>
+        <v>102730.85518802548</v>
       </c>
     </row>
     <row r="19" spans="2:62" x14ac:dyDescent="0.25">
@@ -2914,23 +2897,21 @@
         <v>-37</v>
       </c>
       <c r="Z19" s="2">
-        <f t="shared" ref="Z19:AD19" si="39">+Y19</f>
+        <v>-36</v>
+      </c>
+      <c r="AA19" s="2">
+        <f t="shared" ref="AA19:AD19" si="34">+Z19</f>
+        <v>-36</v>
+      </c>
+      <c r="AB19" s="2">
         <v>-37</v>
       </c>
-      <c r="AA19" s="2">
-        <f t="shared" si="39"/>
+      <c r="AC19" s="2">
+        <f t="shared" si="34"/>
         <v>-37</v>
       </c>
-      <c r="AB19" s="2">
-        <f t="shared" si="39"/>
-        <v>-37</v>
-      </c>
-      <c r="AC19" s="2">
-        <f t="shared" si="39"/>
-        <v>-37</v>
-      </c>
       <c r="AD19" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="34"/>
         <v>-37</v>
       </c>
       <c r="AR19" s="3">
@@ -2960,7 +2941,7 @@
         <v>91</v>
       </c>
       <c r="AY19" s="3">
-        <f t="shared" ref="AY19" si="40">SUM(S19:V19)</f>
+        <f t="shared" ref="AY19" si="35">SUM(S19:V19)</f>
         <v>89</v>
       </c>
     </row>
@@ -2982,148 +2963,148 @@
         <v>948</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" ref="N20" si="41">N18+N19</f>
+        <f t="shared" ref="N20" si="36">N18+N19</f>
         <v>890</v>
       </c>
       <c r="O20" s="10">
-        <f t="shared" ref="O20:U20" si="42">O18+O19</f>
+        <f t="shared" ref="O20:U20" si="37">O18+O19</f>
         <v>686</v>
       </c>
       <c r="P20" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>683</v>
       </c>
       <c r="Q20" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>907</v>
       </c>
       <c r="R20" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>993</v>
       </c>
       <c r="S20" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>673</v>
       </c>
       <c r="T20" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>898</v>
       </c>
       <c r="U20" s="10">
-        <f t="shared" si="42"/>
+        <f t="shared" si="37"/>
         <v>1308</v>
       </c>
       <c r="V20" s="10">
-        <f t="shared" ref="V20:AD20" si="43">V18+V19</f>
+        <f t="shared" ref="V20:AD20" si="38">V18+V19</f>
         <v>1648</v>
       </c>
       <c r="W20" s="10">
-        <f t="shared" ref="W20" si="44">W18+W19</f>
+        <f t="shared" ref="W20" si="39">W18+W19</f>
         <v>1397</v>
       </c>
       <c r="X20" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="38"/>
         <v>501</v>
       </c>
       <c r="Y20" s="10">
-        <f t="shared" si="43"/>
+        <f t="shared" si="38"/>
         <v>1795</v>
       </c>
       <c r="Z20" s="10">
-        <f t="shared" si="43"/>
-        <v>2416.9</v>
+        <f t="shared" si="38"/>
+        <v>2273</v>
       </c>
       <c r="AA20" s="10">
-        <f t="shared" si="43"/>
-        <v>1866.6</v>
+        <f t="shared" si="38"/>
+        <v>1991</v>
       </c>
       <c r="AB20" s="10">
-        <f t="shared" si="43"/>
-        <v>1935.7000000000007</v>
+        <f t="shared" si="38"/>
+        <v>2497</v>
       </c>
       <c r="AC20" s="10">
-        <f t="shared" si="43"/>
-        <v>2818.6038000000008</v>
+        <f t="shared" si="38"/>
+        <v>3454.2000000000007</v>
       </c>
       <c r="AD20" s="10">
-        <f t="shared" si="43"/>
-        <v>4266.7271999999994</v>
+        <f t="shared" si="38"/>
+        <v>3899.2400000000007</v>
       </c>
       <c r="AR20" s="3">
-        <f t="shared" ref="AR20:BA20" si="45">+AR18+AR19</f>
+        <f t="shared" ref="AR20:BA20" si="40">+AR18+AR19</f>
         <v>30</v>
       </c>
       <c r="AS20" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="40"/>
         <v>330</v>
       </c>
       <c r="AT20" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="40"/>
         <v>312</v>
       </c>
       <c r="AU20" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="40"/>
         <v>1275</v>
       </c>
       <c r="AV20" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="40"/>
         <v>3657</v>
       </c>
       <c r="AW20" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="40"/>
         <v>4630</v>
       </c>
       <c r="AX20" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="40"/>
         <v>3269</v>
       </c>
       <c r="AY20" s="3">
-        <f t="shared" si="45"/>
+        <f t="shared" si="40"/>
         <v>4527</v>
       </c>
       <c r="AZ20" s="3">
-        <f t="shared" si="45"/>
-        <v>7864.52</v>
+        <f t="shared" si="40"/>
+        <v>8195.77</v>
       </c>
       <c r="BA20" s="3">
-        <f t="shared" si="45"/>
-        <v>11284.674500000001</v>
+        <f t="shared" si="40"/>
+        <v>14351.969999999998</v>
       </c>
       <c r="BB20" s="3">
-        <f t="shared" ref="BB20:BJ20" si="46">+BB18+BB19</f>
-        <v>17154.738190000004</v>
+        <f t="shared" ref="BB20:BJ20" si="41">+BB18+BB19</f>
+        <v>21641.017</v>
       </c>
       <c r="BC20" s="3">
-        <f t="shared" si="46"/>
-        <v>25982.606369000008</v>
+        <f t="shared" si="41"/>
+        <v>32585.893700000008</v>
       </c>
       <c r="BD20" s="3">
-        <f t="shared" si="46"/>
-        <v>36582.310660900002</v>
+        <f t="shared" si="41"/>
+        <v>45722.854944999992</v>
       </c>
       <c r="BE20" s="3">
-        <f t="shared" si="46"/>
-        <v>51442.562843989988</v>
+        <f t="shared" si="41"/>
+        <v>64124.861064499986</v>
       </c>
       <c r="BF20" s="3">
-        <f t="shared" si="46"/>
-        <v>71200.515669139495</v>
+        <f t="shared" si="41"/>
+        <v>84516.928800674999</v>
       </c>
       <c r="BG20" s="3">
-        <f t="shared" si="46"/>
-        <v>74760.541452596473</v>
+        <f t="shared" si="41"/>
+        <v>88742.775240708754</v>
       </c>
       <c r="BH20" s="3">
-        <f t="shared" si="46"/>
-        <v>78498.568525226292</v>
+        <f t="shared" si="41"/>
+        <v>93179.91400274419</v>
       </c>
       <c r="BI20" s="3">
-        <f t="shared" si="46"/>
-        <v>82423.496951487614</v>
+        <f t="shared" si="41"/>
+        <v>97838.909702881414</v>
       </c>
       <c r="BJ20" s="3">
-        <f t="shared" si="46"/>
-        <v>86544.671799061995</v>
+        <f t="shared" si="41"/>
+        <v>102730.85518802548</v>
       </c>
     </row>
     <row r="21" spans="2:62" x14ac:dyDescent="0.25">
@@ -3176,24 +3157,21 @@
         <v>153</v>
       </c>
       <c r="Z21" s="10">
-        <f t="shared" ref="Z21:AD21" si="47">+Z20*0.1</f>
-        <v>241.69000000000003</v>
+        <v>455</v>
       </c>
       <c r="AA21" s="10">
-        <f t="shared" si="47"/>
-        <v>186.66</v>
+        <v>238</v>
       </c>
       <c r="AB21" s="10">
-        <f t="shared" si="47"/>
-        <v>193.57000000000008</v>
+        <v>252</v>
       </c>
       <c r="AC21" s="10">
-        <f t="shared" si="47"/>
-        <v>281.86038000000008</v>
+        <f t="shared" ref="AC21:AD21" si="42">+AC20*0.1</f>
+        <v>345.42000000000007</v>
       </c>
       <c r="AD21" s="10">
-        <f t="shared" si="47"/>
-        <v>426.67271999999997</v>
+        <f t="shared" si="42"/>
+        <v>389.92400000000009</v>
       </c>
       <c r="AR21" s="3">
         <f>9+2</f>
@@ -3219,52 +3197,52 @@
         <v>346</v>
       </c>
       <c r="AY21" s="3">
-        <f t="shared" ref="AY21" si="48">SUM(S21:V21)</f>
+        <f t="shared" ref="AY21" si="43">SUM(S21:V21)</f>
         <v>485</v>
       </c>
       <c r="AZ21" s="3">
         <f>+AZ20*0.15</f>
-        <v>1179.6780000000001</v>
+        <v>1229.3655000000001</v>
       </c>
       <c r="BA21" s="3">
         <f>+BA20*0.15</f>
-        <v>1692.7011750000001</v>
+        <v>2152.7954999999997</v>
       </c>
       <c r="BB21" s="3">
-        <f t="shared" ref="BB21:BJ21" si="49">+BB20*0.15</f>
-        <v>2573.2107285000006</v>
+        <f t="shared" ref="BB21:BJ21" si="44">+BB20*0.15</f>
+        <v>3246.1525499999998</v>
       </c>
       <c r="BC21" s="3">
-        <f t="shared" si="49"/>
-        <v>3897.3909553500011</v>
+        <f t="shared" si="44"/>
+        <v>4887.8840550000014</v>
       </c>
       <c r="BD21" s="3">
-        <f t="shared" si="49"/>
-        <v>5487.3465991350004</v>
+        <f t="shared" si="44"/>
+        <v>6858.428241749999</v>
       </c>
       <c r="BE21" s="3">
-        <f t="shared" si="49"/>
-        <v>7716.3844265984981</v>
+        <f t="shared" si="44"/>
+        <v>9618.7291596749983</v>
       </c>
       <c r="BF21" s="3">
-        <f t="shared" si="49"/>
-        <v>10680.077350370924</v>
+        <f t="shared" si="44"/>
+        <v>12677.53932010125</v>
       </c>
       <c r="BG21" s="3">
-        <f t="shared" si="49"/>
-        <v>11214.08121788947</v>
+        <f t="shared" si="44"/>
+        <v>13311.416286106312</v>
       </c>
       <c r="BH21" s="3">
-        <f t="shared" si="49"/>
-        <v>11774.785278783944</v>
+        <f t="shared" si="44"/>
+        <v>13976.987100411628</v>
       </c>
       <c r="BI21" s="3">
-        <f t="shared" si="49"/>
-        <v>12363.524542723142</v>
+        <f t="shared" si="44"/>
+        <v>14675.836455432212</v>
       </c>
       <c r="BJ21" s="3">
-        <f t="shared" si="49"/>
-        <v>12981.700769859299</v>
+        <f t="shared" si="44"/>
+        <v>15409.628278203822</v>
       </c>
     </row>
     <row r="22" spans="2:62" x14ac:dyDescent="0.25">
@@ -3285,148 +3263,148 @@
         <v>935</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" ref="N22" si="50">N20-N21</f>
+        <f t="shared" ref="N22" si="45">N20-N21</f>
         <v>890</v>
       </c>
       <c r="O22" s="10">
-        <f t="shared" ref="O22:U22" si="51">O20-O21</f>
+        <f t="shared" ref="O22:U22" si="46">O20-O21</f>
         <v>673</v>
       </c>
       <c r="P22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>706</v>
       </c>
       <c r="Q22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>946</v>
       </c>
       <c r="R22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>598</v>
       </c>
       <c r="S22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>621</v>
       </c>
       <c r="T22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>857</v>
       </c>
       <c r="U22" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="46"/>
         <v>1335</v>
       </c>
       <c r="V22" s="10">
-        <f t="shared" ref="V22:AD22" si="52">V20-V21</f>
+        <f t="shared" ref="V22:AD22" si="47">V20-V21</f>
         <v>1229</v>
       </c>
       <c r="W22" s="10">
-        <f t="shared" ref="W22" si="53">W20-W21</f>
+        <f t="shared" ref="W22" si="48">W20-W21</f>
         <v>1274</v>
       </c>
       <c r="X22" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>501</v>
       </c>
       <c r="Y22" s="10">
-        <f t="shared" si="52"/>
+        <f t="shared" si="47"/>
         <v>1642</v>
       </c>
       <c r="Z22" s="10">
-        <f t="shared" si="52"/>
-        <v>2175.21</v>
+        <f t="shared" si="47"/>
+        <v>1818</v>
       </c>
       <c r="AA22" s="10">
-        <f t="shared" si="52"/>
-        <v>1679.9399999999998</v>
+        <f t="shared" si="47"/>
+        <v>1753</v>
       </c>
       <c r="AB22" s="10">
-        <f t="shared" si="52"/>
-        <v>1742.1300000000006</v>
+        <f t="shared" si="47"/>
+        <v>2245</v>
       </c>
       <c r="AC22" s="10">
-        <f t="shared" si="52"/>
-        <v>2536.7434200000007</v>
+        <f t="shared" si="47"/>
+        <v>3108.7800000000007</v>
       </c>
       <c r="AD22" s="10">
-        <f t="shared" si="52"/>
-        <v>3840.0544799999993</v>
+        <f t="shared" si="47"/>
+        <v>3509.3160000000007</v>
       </c>
       <c r="AR22" s="3">
-        <f t="shared" ref="AR22:BA22" si="54">+AR20-AR21</f>
+        <f t="shared" ref="AR22:BA22" si="49">+AR20-AR21</f>
         <v>19</v>
       </c>
       <c r="AS22" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>319</v>
       </c>
       <c r="AT22" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>312</v>
       </c>
       <c r="AU22" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>1275</v>
       </c>
       <c r="AV22" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>3144</v>
       </c>
       <c r="AW22" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>4630</v>
       </c>
       <c r="AX22" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>2923</v>
       </c>
       <c r="AY22" s="3">
-        <f t="shared" si="54"/>
+        <f t="shared" si="49"/>
         <v>4042</v>
       </c>
       <c r="AZ22" s="3">
-        <f t="shared" si="54"/>
-        <v>6684.8420000000006</v>
+        <f t="shared" si="49"/>
+        <v>6966.4045000000006</v>
       </c>
       <c r="BA22" s="3">
-        <f t="shared" si="54"/>
-        <v>9591.9733250000008</v>
+        <f t="shared" si="49"/>
+        <v>12199.174499999997</v>
       </c>
       <c r="BB22" s="3">
-        <f t="shared" ref="BB22:BJ22" si="55">+BB20-BB21</f>
-        <v>14581.527461500003</v>
+        <f t="shared" ref="BB22:BJ22" si="50">+BB20-BB21</f>
+        <v>18394.864450000001</v>
       </c>
       <c r="BC22" s="3">
-        <f t="shared" si="55"/>
-        <v>22085.215413650007</v>
+        <f t="shared" si="50"/>
+        <v>27698.009645000006</v>
       </c>
       <c r="BD22" s="3">
-        <f t="shared" si="55"/>
-        <v>31094.964061765</v>
+        <f t="shared" si="50"/>
+        <v>38864.426703249992</v>
       </c>
       <c r="BE22" s="3">
-        <f t="shared" si="55"/>
-        <v>43726.178417391493</v>
+        <f t="shared" si="50"/>
+        <v>54506.131904824986</v>
       </c>
       <c r="BF22" s="3">
-        <f t="shared" si="55"/>
-        <v>60520.438318768574</v>
+        <f t="shared" si="50"/>
+        <v>71839.389480573751</v>
       </c>
       <c r="BG22" s="3">
-        <f t="shared" si="55"/>
-        <v>63546.460234707003</v>
+        <f t="shared" si="50"/>
+        <v>75431.358954602445</v>
       </c>
       <c r="BH22" s="3">
-        <f t="shared" si="55"/>
-        <v>66723.783246442355</v>
+        <f t="shared" si="50"/>
+        <v>79202.926902332561</v>
       </c>
       <c r="BI22" s="3">
-        <f t="shared" si="55"/>
-        <v>70059.972408764472</v>
+        <f t="shared" si="50"/>
+        <v>83163.073247449196</v>
       </c>
       <c r="BJ22" s="3">
-        <f t="shared" si="55"/>
-        <v>73562.971029202701</v>
+        <f t="shared" si="50"/>
+        <v>87321.226909821664</v>
       </c>
     </row>
     <row r="23" spans="2:62" x14ac:dyDescent="0.25">
@@ -3435,160 +3413,160 @@
       </c>
       <c r="J23" s="11"/>
       <c r="K23" s="11">
-        <f t="shared" ref="K23:U23" si="56">K22/K24</f>
+        <f t="shared" ref="K23:U23" si="51">K22/K24</f>
         <v>0.83617021276595749</v>
       </c>
       <c r="L23" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0.89460784313725494</v>
       </c>
       <c r="M23" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0.58038485412787089</v>
       </c>
       <c r="N23" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0.56651814131126665</v>
       </c>
       <c r="O23" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0.41775294847920547</v>
       </c>
       <c r="P23" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0.4339274738783036</v>
       </c>
       <c r="Q23" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0.58072437077961936</v>
       </c>
       <c r="R23" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0.36799999999999999</v>
       </c>
       <c r="S23" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0.37888956680902991</v>
       </c>
       <c r="T23" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0.52351863164324985</v>
       </c>
       <c r="U23" s="11">
-        <f t="shared" si="56"/>
+        <f t="shared" si="51"/>
         <v>0.81601466992665039</v>
       </c>
       <c r="V23" s="11">
-        <f t="shared" ref="V23:AD23" si="57">V22/V24</f>
+        <f t="shared" ref="V23:AD23" si="52">V22/V24</f>
         <v>0.75214198286413714</v>
       </c>
       <c r="W23" s="11">
-        <f t="shared" ref="W23" si="58">W22/W24</f>
+        <f t="shared" ref="W23" si="53">W22/W24</f>
         <v>0.78351783517835183</v>
       </c>
       <c r="X23" s="11">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>0.30736196319018405</v>
       </c>
       <c r="Y23" s="11">
-        <f t="shared" si="57"/>
+        <f t="shared" si="52"/>
         <v>1.0006093845216331</v>
       </c>
       <c r="Z23" s="11">
-        <f t="shared" si="57"/>
-        <v>1.3255393053016453</v>
+        <f t="shared" si="52"/>
+        <v>1.1024863553668891</v>
       </c>
       <c r="AA23" s="11">
-        <f t="shared" si="57"/>
-        <v>1.0237294332723947</v>
+        <f t="shared" si="52"/>
+        <v>1.0624242424242425</v>
       </c>
       <c r="AB23" s="11">
-        <f t="shared" si="57"/>
-        <v>1.0616270566727608</v>
+        <f t="shared" si="52"/>
+        <v>1.3532248342374924</v>
       </c>
       <c r="AC23" s="11">
-        <f t="shared" si="57"/>
-        <v>1.5458521755027426</v>
+        <f t="shared" si="52"/>
+        <v>1.8738878842676314</v>
       </c>
       <c r="AD23" s="11">
-        <f t="shared" si="57"/>
-        <v>2.3400697623400362</v>
+        <f t="shared" si="52"/>
+        <v>2.115320072332731</v>
       </c>
       <c r="AR23" s="1">
-        <f t="shared" ref="AR23:BA23" si="59">+AR22/AR24</f>
+        <f t="shared" ref="AR23:BA23" si="54">+AR22/AR24</f>
         <v>1.9957983193277309E-2</v>
       </c>
       <c r="AS23" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="54"/>
         <v>0.29981203007518797</v>
       </c>
       <c r="AT23" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="54"/>
         <v>0.27857142857142858</v>
       </c>
       <c r="AU23" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="54"/>
         <v>1.056338028169014</v>
       </c>
       <c r="AV23" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="54"/>
         <v>2.5581773799837264</v>
       </c>
       <c r="AW23" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="54"/>
         <v>2.9471674092934435</v>
       </c>
       <c r="AX23" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="54"/>
         <v>1.7987692307692307</v>
       </c>
       <c r="AY23" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="54"/>
         <v>2.4699052856706385</v>
       </c>
       <c r="AZ23" s="1">
-        <f t="shared" si="59"/>
-        <v>4.0848408188206538</v>
+        <f t="shared" si="54"/>
+        <v>4.2568924534066612</v>
       </c>
       <c r="BA23" s="1">
-        <f t="shared" si="59"/>
-        <v>5.8612730369691421</v>
+        <f t="shared" si="54"/>
+        <v>7.4544298808432616</v>
       </c>
       <c r="BB23" s="1">
-        <f t="shared" ref="BB23:BJ23" si="60">+BB22/BB24</f>
-        <v>8.9101909327833813</v>
+        <f t="shared" ref="BB23:BJ23" si="55">+BB22/BB24</f>
+        <v>11.240369355331501</v>
       </c>
       <c r="BC23" s="1">
-        <f t="shared" si="60"/>
-        <v>13.495395914237706</v>
+        <f t="shared" si="55"/>
+        <v>16.925151020470519</v>
       </c>
       <c r="BD23" s="1">
-        <f t="shared" si="60"/>
-        <v>19.000894629859456</v>
+        <f t="shared" si="55"/>
+        <v>23.748503943324163</v>
       </c>
       <c r="BE23" s="1">
-        <f t="shared" si="60"/>
-        <v>26.719326866722575</v>
+        <f t="shared" si="55"/>
+        <v>33.306527286785816</v>
       </c>
       <c r="BF23" s="1">
-        <f t="shared" si="60"/>
-        <v>36.98163050337218</v>
+        <f t="shared" si="55"/>
+        <v>43.898190944438589</v>
       </c>
       <c r="BG23" s="1">
-        <f t="shared" si="60"/>
-        <v>38.830712028540788</v>
+        <f t="shared" si="55"/>
+        <v>46.093100491660522</v>
       </c>
       <c r="BH23" s="1">
-        <f t="shared" si="60"/>
-        <v>40.772247629967829</v>
+        <f t="shared" si="55"/>
+        <v>48.397755516243542</v>
       </c>
       <c r="BI23" s="1">
-        <f t="shared" si="60"/>
-        <v>42.810860011466225</v>
+        <f t="shared" si="55"/>
+        <v>50.817643292055727</v>
       </c>
       <c r="BJ23" s="1">
-        <f t="shared" si="60"/>
-        <v>44.951403012039535</v>
+        <f t="shared" si="55"/>
+        <v>53.358525456658519</v>
       </c>
     </row>
     <row r="24" spans="2:62" x14ac:dyDescent="0.25">
@@ -3644,24 +3622,21 @@
         <v>1641</v>
       </c>
       <c r="Z24" s="10">
-        <f t="shared" ref="Z24:AD24" si="61">+Y24</f>
-        <v>1641</v>
+        <v>1649</v>
       </c>
       <c r="AA24" s="10">
-        <f t="shared" si="61"/>
-        <v>1641</v>
+        <v>1650</v>
       </c>
       <c r="AB24" s="10">
-        <f t="shared" si="61"/>
-        <v>1641</v>
+        <v>1659</v>
       </c>
       <c r="AC24" s="10">
-        <f t="shared" si="61"/>
-        <v>1641</v>
+        <f t="shared" ref="AC24:AD24" si="56">+AB24</f>
+        <v>1659</v>
       </c>
       <c r="AD24" s="10">
-        <f t="shared" si="61"/>
-        <v>1641</v>
+        <f t="shared" si="56"/>
+        <v>1659</v>
       </c>
       <c r="AR24" s="3">
         <v>952</v>
@@ -3697,39 +3672,39 @@
         <v>1636.5</v>
       </c>
       <c r="BB24" s="3">
-        <f t="shared" ref="BB24:BJ24" si="62">+BA24</f>
+        <f t="shared" ref="BB24:BJ24" si="57">+BA24</f>
         <v>1636.5</v>
       </c>
       <c r="BC24" s="3">
-        <f t="shared" si="62"/>
+        <f t="shared" si="57"/>
         <v>1636.5</v>
       </c>
       <c r="BD24" s="3">
-        <f t="shared" si="62"/>
+        <f t="shared" si="57"/>
         <v>1636.5</v>
       </c>
       <c r="BE24" s="3">
-        <f t="shared" si="62"/>
+        <f t="shared" si="57"/>
         <v>1636.5</v>
       </c>
       <c r="BF24" s="3">
-        <f t="shared" si="62"/>
+        <f t="shared" si="57"/>
         <v>1636.5</v>
       </c>
       <c r="BG24" s="3">
-        <f t="shared" si="62"/>
+        <f t="shared" si="57"/>
         <v>1636.5</v>
       </c>
       <c r="BH24" s="3">
-        <f t="shared" si="62"/>
+        <f t="shared" si="57"/>
         <v>1636.5</v>
       </c>
       <c r="BI24" s="3">
-        <f t="shared" si="62"/>
+        <f t="shared" si="57"/>
         <v>1636.5</v>
       </c>
       <c r="BJ24" s="3">
-        <f t="shared" si="62"/>
+        <f t="shared" si="57"/>
         <v>1636.5</v>
       </c>
     </row>
@@ -3743,103 +3718,103 @@
         <v>-9.0708340411075228E-2</v>
       </c>
       <c r="P27" s="12">
-        <f t="shared" ref="P27:Z27" si="63">P12/L12-1</f>
+        <f t="shared" ref="P27:Z27" si="58">P12/L12-1</f>
         <v>-0.18183206106870231</v>
       </c>
       <c r="Q27" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>4.2228212039532753E-2</v>
       </c>
       <c r="R27" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>0.10162529023039824</v>
       </c>
       <c r="S27" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>2.2417336073230043E-2</v>
       </c>
       <c r="T27" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>8.882254151894009E-2</v>
       </c>
       <c r="U27" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>0.17568965517241386</v>
       </c>
       <c r="V27" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>0.24156939040207526</v>
       </c>
       <c r="W27" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>0.35903526402338759</v>
       </c>
       <c r="X27" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>0.31705227077977716</v>
       </c>
       <c r="Y27" s="12">
-        <f t="shared" si="63"/>
+        <f t="shared" si="58"/>
         <v>0.35591728992520899</v>
       </c>
       <c r="Z27" s="12">
-        <f t="shared" si="63"/>
-        <v>0.2594672238182294</v>
+        <f t="shared" si="58"/>
+        <v>0.34108122225124049</v>
       </c>
       <c r="AA27" s="12">
-        <f t="shared" ref="AA27" si="64">AA12/W12-1</f>
-        <v>0.18983597741328317</v>
+        <f>AA12/W12-1</f>
+        <v>0.37846195213767131</v>
       </c>
       <c r="AB27" s="12">
-        <f t="shared" ref="AB27" si="65">AB12/X12-1</f>
-        <v>0.24007807417046201</v>
+        <f>AB12/X12-1</f>
+        <v>0.5011060507482108</v>
       </c>
       <c r="AC27" s="12">
-        <f t="shared" ref="AC27" si="66">AC12/Y12-1</f>
-        <v>0.27871187540558084</v>
+        <f t="shared" ref="AC27" si="59">AC12/Y12-1</f>
+        <v>0.40601341120484524</v>
       </c>
       <c r="AD27" s="12">
-        <f t="shared" ref="AD27" si="67">AD12/Z12-1</f>
-        <v>0.4080539139450492</v>
+        <f t="shared" ref="AD27" si="60">AD12/Z12-1</f>
+        <v>0.40954235637779934</v>
       </c>
       <c r="AO27" s="7">
-        <f t="shared" ref="AO27:AR27" si="68">+AO12/AN12-1</f>
+        <f t="shared" ref="AO27:AR27" si="61">+AO12/AN12-1</f>
         <v>3.9063974334780038E-2</v>
       </c>
       <c r="AP27" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="61"/>
         <v>-0.27515437704322554</v>
       </c>
       <c r="AQ27" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="61"/>
         <v>7.0408418942620843E-2</v>
       </c>
       <c r="AR27" s="7">
-        <f t="shared" si="68"/>
+        <f t="shared" si="61"/>
         <v>0.24742509363295873</v>
       </c>
       <c r="AS27" s="7">
-        <f t="shared" ref="AS27:AX27" si="69">+AS12/AR12-1</f>
+        <f t="shared" ref="AS27:AX27" si="62">+AS12/AR12-1</f>
         <v>0.21504972790392185</v>
       </c>
       <c r="AT27" s="7">
-        <f t="shared" si="69"/>
+        <f t="shared" si="62"/>
         <v>3.9536679536679609E-2</v>
       </c>
       <c r="AU27" s="7">
-        <f t="shared" si="69"/>
+        <f t="shared" si="62"/>
         <v>0.45045312732134901</v>
       </c>
       <c r="AV27" s="7">
-        <f t="shared" si="69"/>
+        <f t="shared" si="62"/>
         <v>0.68329406944586712</v>
       </c>
       <c r="AW27" s="7">
-        <f t="shared" si="69"/>
+        <f t="shared" si="62"/>
         <v>0.43610806863818907</v>
       </c>
       <c r="AX27" s="7">
-        <f t="shared" si="69"/>
+        <f t="shared" si="62"/>
         <v>-3.9023770179229644E-2</v>
       </c>
       <c r="AY27" s="7">
@@ -3848,46 +3823,46 @@
       </c>
       <c r="AZ27" s="7">
         <f>+AZ12/AY12-1</f>
-        <v>0.31913903432228041</v>
+        <v>0.3433779329067288</v>
       </c>
       <c r="BA27" s="7">
         <f>+BA12/AZ12-1</f>
-        <v>0.24609425530663853</v>
+        <v>0.39068679811772866</v>
       </c>
       <c r="BB27" s="7">
-        <f t="shared" ref="BB27:BJ27" si="70">+BB12/BA12-1</f>
-        <v>0.31107660438389861</v>
+        <f t="shared" ref="BB27:BJ27" si="63">+BB12/BA12-1</f>
+        <v>0.32928257078800982</v>
       </c>
       <c r="BC27" s="7">
-        <f t="shared" si="70"/>
-        <v>0.34149230145452214</v>
+        <f t="shared" si="63"/>
+        <v>0.35872892922844368</v>
       </c>
       <c r="BD27" s="7">
-        <f t="shared" si="70"/>
-        <v>0.30251986451339863</v>
+        <f t="shared" si="63"/>
+        <v>0.3142223066872385</v>
       </c>
       <c r="BE27" s="7">
-        <f t="shared" si="70"/>
-        <v>0.3176763810237011</v>
+        <f t="shared" si="63"/>
+        <v>0.32820433638668067</v>
       </c>
       <c r="BF27" s="7">
-        <f t="shared" si="70"/>
+        <f t="shared" si="63"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BG27" s="7">
-        <f t="shared" si="70"/>
+        <f t="shared" si="63"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BH27" s="7">
-        <f t="shared" si="70"/>
+        <f t="shared" si="63"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BI27" s="7">
-        <f t="shared" si="70"/>
+        <f t="shared" si="63"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BJ27" s="7">
-        <f t="shared" si="70"/>
+        <f t="shared" si="63"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -3897,159 +3872,159 @@
       </c>
       <c r="J28" s="12"/>
       <c r="K28" s="12">
-        <f t="shared" ref="K28:Z28" si="71">K14/K12</f>
+        <f t="shared" ref="K28:Z28" si="64">K14/K12</f>
         <v>0.51027688126380155</v>
       </c>
       <c r="L28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
         <v>0.52442748091603053</v>
       </c>
       <c r="M28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
         <v>0.49703504043126684</v>
       </c>
       <c r="N28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
         <v>0.5083050544740132</v>
       </c>
       <c r="O28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
         <v>0.49766486082570521</v>
       </c>
       <c r="P28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
         <v>0.49542825153946629</v>
       </c>
       <c r="Q28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
         <v>0.5098275862068965</v>
       </c>
       <c r="R28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
         <v>0.50680933852140075</v>
       </c>
       <c r="S28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
         <v>0.5097752603690846</v>
       </c>
       <c r="T28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
         <v>0.53144815766923736</v>
       </c>
       <c r="U28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
         <v>0.53556239917876525</v>
       </c>
       <c r="V28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
         <v>0.53982763123530952</v>
       </c>
       <c r="W28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
         <v>0.53670341489647755</v>
       </c>
       <c r="X28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
         <v>0.43279115159401432</v>
       </c>
       <c r="Y28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
         <v>0.54510058403633999</v>
       </c>
       <c r="Z28" s="12">
-        <f t="shared" si="71"/>
+        <f t="shared" si="64"/>
+        <v>0.56835443037974687</v>
+      </c>
+      <c r="AA28" s="12">
+        <f t="shared" ref="AA28:AD28" si="65">AA14/AA12</f>
+        <v>0.55369160245781723</v>
+      </c>
+      <c r="AB28" s="12">
+        <f t="shared" si="65"/>
+        <v>0.56024618585298191</v>
+      </c>
+      <c r="AC28" s="12">
+        <f t="shared" si="65"/>
         <v>0.54</v>
       </c>
-      <c r="AA28" s="12">
-        <f t="shared" ref="AA28:AD28" si="72">AA14/AA12</f>
+      <c r="AD28" s="12">
+        <f t="shared" si="65"/>
         <v>0.54</v>
       </c>
-      <c r="AB28" s="12">
-        <f t="shared" si="72"/>
-        <v>0.54</v>
-      </c>
-      <c r="AC28" s="12">
-        <f t="shared" si="72"/>
-        <v>0.54</v>
-      </c>
-      <c r="AD28" s="12">
-        <f t="shared" si="72"/>
-        <v>0.54</v>
-      </c>
       <c r="AR28" s="7">
-        <f t="shared" ref="AR28:BA28" si="73">+AR14/AR12</f>
+        <f t="shared" ref="AR28:BA28" si="66">+AR14/AR12</f>
         <v>0.3495965471945956</v>
       </c>
       <c r="AS28" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="66"/>
         <v>0.37791505791505792</v>
       </c>
       <c r="AT28" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="66"/>
         <v>0.42608824840291187</v>
       </c>
       <c r="AU28" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="66"/>
         <v>0.44525248386766364</v>
       </c>
       <c r="AV28" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="66"/>
         <v>0.48247535596933189</v>
       </c>
       <c r="AW28" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="66"/>
         <v>0.51061395703571888</v>
       </c>
       <c r="AX28" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="66"/>
         <v>0.5027336860670194</v>
       </c>
       <c r="AY28" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="66"/>
         <v>0.53042466550319955</v>
       </c>
       <c r="AZ28" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="66"/>
         <v>0.53</v>
       </c>
       <c r="BA28" s="7">
-        <f t="shared" si="73"/>
+        <f t="shared" si="66"/>
         <v>0.53</v>
       </c>
       <c r="BB28" s="7">
-        <f t="shared" ref="BB28:BJ28" si="74">+BB14/BB12</f>
+        <f t="shared" ref="BB28:BJ28" si="67">+BB14/BB12</f>
         <v>0.53</v>
       </c>
       <c r="BC28" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="67"/>
         <v>0.53</v>
       </c>
       <c r="BD28" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="67"/>
         <v>0.53</v>
       </c>
       <c r="BE28" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="67"/>
         <v>0.53</v>
       </c>
       <c r="BF28" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="67"/>
         <v>0.53</v>
       </c>
       <c r="BG28" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="67"/>
         <v>0.53</v>
       </c>
       <c r="BH28" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="67"/>
         <v>0.53</v>
       </c>
       <c r="BI28" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="67"/>
         <v>0.53</v>
       </c>
       <c r="BJ28" s="7">
-        <f t="shared" si="74"/>
+        <f t="shared" si="67"/>
         <v>0.53</v>
       </c>
     </row>
@@ -4947,23 +4922,23 @@
       <c r="AF59" s="10"/>
       <c r="AG59" s="10"/>
       <c r="AS59" s="3">
-        <f t="shared" ref="AS59:AW59" si="75">+AS57-AS58</f>
+        <f t="shared" ref="AS59:AW59" si="68">+AS57-AS58</f>
         <v>-129</v>
       </c>
       <c r="AT59" s="3">
-        <f t="shared" si="75"/>
+        <f t="shared" si="68"/>
         <v>344</v>
       </c>
       <c r="AU59" s="3">
-        <f t="shared" si="75"/>
+        <f t="shared" si="68"/>
         <v>777</v>
       </c>
       <c r="AV59" s="3">
-        <f t="shared" si="75"/>
+        <f t="shared" si="68"/>
         <v>3220</v>
       </c>
       <c r="AW59" s="3">
-        <f t="shared" si="75"/>
+        <f t="shared" si="68"/>
         <v>3115</v>
       </c>
       <c r="AX59" s="3">
